--- a/all/Detail/Generation consistency scores.xlsx
+++ b/all/Detail/Generation consistency scores.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\工作\研究生\sjy论文\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzk\Desktop\Detail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3724AB-B9F3-45A6-B1A8-4ABD9C2884CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216543C0-6C42-44CF-972B-39AE9A93ABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,19 +41,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="21">
   <si>
-    <t>DeepSeek-V3.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Qwen3.5-Plus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ChatGPT-4.0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gemini3.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -120,7 +108,17 @@
     <t>Plot with one decimal place retained</t>
   </si>
   <si>
-    <t>Scores were assigned on a 0–100 scale. No response received a full score, as at least one dimension showed a minor inconsistency in every case.</t>
+    <t>Each test response was assigned a single overall score on a 0–100 scale, taking all three dimensions into account. Scores were assigned independently by the authors. The reported score is the mean of the 10 test responses for each gas database and model. No response received a full score, as at least one dimension showed a minor inconsistency in every case</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qwen3-Max</t>
+  </si>
+  <si>
+    <t>DeepSeek-V3.1</t>
+  </si>
+  <si>
+    <t>Gemini 3</t>
   </si>
 </sst>
 </file>
@@ -453,207 +451,207 @@
   <sheetData>
     <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" t="s">
+      <c r="W1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="Y1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Z1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" t="s">
+      <c r="AC1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="AE1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AL1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN1" t="s">
         <v>0</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AO1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP1" t="s">
         <v>1</v>
       </c>
-      <c r="V1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W1" t="s">
-        <v>3</v>
-      </c>
-      <c r="X1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AQ1" t="s">
         <v>11</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AR1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT1" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AU1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV1" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE1" t="s">
+      <c r="AW1" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AX1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AZ1" t="s">
         <v>0</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="BA1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BB1" t="s">
         <v>1</v>
       </c>
-      <c r="AH1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK1" t="s">
+      <c r="BC1" t="s">
         <v>13</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="BD1" t="s">
+        <v>19</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BF1" t="s">
         <v>0</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="BG1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BH1" t="s">
         <v>1</v>
       </c>
-      <c r="AN1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ1" t="s">
+      <c r="BI1" t="s">
         <v>14</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BJ1" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>18</v>
+      </c>
+      <c r="BL1" t="s">
         <v>0</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BM1" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN1" t="s">
         <v>1</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>3</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>4</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>16</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>3</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>4</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>17</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>3</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -671,7 +669,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -689,7 +687,7 @@
         <v>100</v>
       </c>
       <c r="M2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>100</v>
@@ -707,7 +705,7 @@
         <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2">
         <v>100</v>
@@ -725,7 +723,7 @@
         <v>100</v>
       </c>
       <c r="Y2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z2">
         <v>100</v>
@@ -743,7 +741,7 @@
         <v>100</v>
       </c>
       <c r="AE2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AF2">
         <v>100</v>
@@ -761,7 +759,7 @@
         <v>100</v>
       </c>
       <c r="AK2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AL2">
         <v>100</v>
@@ -779,7 +777,7 @@
         <v>100</v>
       </c>
       <c r="AQ2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>100</v>
@@ -797,7 +795,7 @@
         <v>100</v>
       </c>
       <c r="AW2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX2">
         <v>100</v>
@@ -815,7 +813,7 @@
         <v>100</v>
       </c>
       <c r="BC2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BD2">
         <v>100</v>
@@ -833,7 +831,7 @@
         <v>100</v>
       </c>
       <c r="BI2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BJ2">
         <v>100</v>
@@ -2553,7 +2551,7 @@
     </row>
     <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13">
         <f>SUM(B3:B12)/10</f>
@@ -2778,7 +2776,7 @@
     </row>
     <row r="15" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <f>SUM(B13+H13+N13+T13+Z13+AF13+AL13+AR13+AX13+BD13+BJ13)/11</f>
@@ -2803,12 +2801,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
